--- a/output/pdf_financials_xlsx/LIVE.xlsx
+++ b/output/pdf_financials_xlsx/LIVE.xlsx
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.026135</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06795900000000001</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -4757,7 +4757,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>-0.026135</v>
       </c>

--- a/output/pdf_financials_xlsx/LIVE.xlsx
+++ b/output/pdf_financials_xlsx/LIVE.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.317979</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.136427</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.123064</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.065217</v>
+        <v>0.383196</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.021739</v>
+        <v>0.158166</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.758</v>
+        <v>0.881064</v>
       </c>
     </row>
     <row r="37">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.331575</v>
+        <v>0.013596</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.136589</v>
+        <v>0.000162</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/LIVE.xlsx
+++ b/output/pdf_financials_xlsx/LIVE.xlsx
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.065777</v>
       </c>
     </row>
     <row r="116">
@@ -4133,7 +4133,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
